--- a/REBOUND Score.xlsx
+++ b/REBOUND Score.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gupta\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A605D441-3A07-4BE6-8CEB-4708B33DDB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4595EB-0817-4B26-978A-064DD3AC6CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BA97016-6CBA-492C-9063-41309AA0924B}"/>
+    <workbookView xWindow="-25710" yWindow="-680" windowWidth="25820" windowHeight="15500" xr2:uid="{9BA97016-6CBA-492C-9063-41309AA0924B}"/>
   </bookViews>
   <sheets>
     <sheet name="EntrySurvey_JaydenUpdated" sheetId="1" r:id="rId1"/>
@@ -754,17 +754,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A24BF24-ED13-4990-982C-9D040FD6312B}">
   <dimension ref="A1:F96"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6328125" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -784,7 +784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -798,7 +798,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -812,7 +812,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -829,7 +829,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -846,7 +846,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -863,7 +863,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -880,7 +880,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -897,7 +897,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -917,7 +917,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -934,7 +934,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -951,7 +951,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -968,7 +968,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -985,7 +985,7 @@
         <v>64.25</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>59.62</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>89.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>41.75</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>58.62</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>37.380000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>74.38</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>51.25</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>47</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>48</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>74.25</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>68.38</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>62.88</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>86.38</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>86.75</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>70</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>85.31</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>71</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>46.22</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>72</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>47.47</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>75</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>89.58</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>46.22</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>78</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>63.13</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>79</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>80</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>81</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>82</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>83</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>65.14</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>69.38</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>63.88</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>86</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>87</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>88</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>89</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>90</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>91</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>92</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>65.13</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>93</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>53.63</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>94</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>73.25</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>95</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>90.13</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>96</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>97</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>98</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>99</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>71.63</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>100</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>101</v>
       </c>
@@ -2401,9 +2401,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC7A1BD-3142-4417-A0E5-169F8860780E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>109</v>
       </c>
